--- a/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.92</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>0.6389</v>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6897</v>
+        <v>0.6552</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.5714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8919</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8</v>
+        <v>0.7895</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8717</v>
+        <v>0.8497</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9565</v>
+        <v>0.913</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1</v>
+        <v>0.1111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -645,13 +645,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>0.5833</v>
       </c>
     </row>
     <row r="3">
@@ -686,16 +686,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4286</v>
+        <v>0.5714</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.92</v>
+        <v>0.8846000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -883,16 +883,16 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
         <v>23</v>
@@ -905,22 +905,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>23</v>
@@ -936,7 +936,7 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
         <v>23</v>
@@ -967,16 +967,16 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>23</v>
@@ -992,7 +992,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
         <v>23</v>
@@ -1004,7 +1004,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
         <v>23</v>
@@ -1026,7 +1026,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
@@ -1341,7 +1341,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8248</v>
+        <v>0.8232</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquesta funcionalitat es connecta viasocket amb el servidor i mostra el contingut segons els missatges que aquest envia.</t>
+          <t>The application connects via socket with the server to show content in real time.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A design pattern that allows adding behavior to an object, used here to extend component functionality for testing.</t>
+          <t>A design pattern that allows adding behavior to an object, used here to facilitate testing tasks.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The layer that contains the business logic, processes information, and performs necessary operations.</t>
+          <t>The layer that contains the business logic, processing information and performing necessary operations.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M06_AU27</t>
+          <t>CF_M06_AU10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.925</v>
+        <v>0.8976</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -1681,28 +1681,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
+          <t>The Dispatcher notifies Stores when the state should be modified.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_03', 'AU_02']</t>
+          <t>['AU_08', 'AU_06']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>presentation layer, waapiti server</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1713,33 +1713,33 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This will interact with the Waapiti API using HTTP requests.</t>
+          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M06_AU01, CF_M06_AU02</t>
+          <t>CF_M06_AU08, CF_M06_AU07</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M06_AU27</t>
+          <t>CF_M06_AU10</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>mobile device, waapiti server</t>
+          <t>action, store</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9258</v>
+        <v>0.9107</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>El servidor que s’encarrega de comunicar-se amb la base de dades i altres serveis allotjats a AWS.</t>
+          <t>The Waapiti Server communicates with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1779,7 +1779,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1821,35 +1821,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
+          <t>CF_M06_AU27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9895</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Mobile Device</t>
-        </is>
-      </c>
+        <v>0.9185</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>The mobile application interacts with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1857,50 +1853,62 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['AU_03', 'AU_02']</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Mobile device</t>
-        </is>
-      </c>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti server</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This is the device where the application will be hosted.</t>
+          <t>This will interact with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>45</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CF_M06_AU01, CF_M06_AU02</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>CF_M06_AU27</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>mobile device, waapiti server</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
+          <t>CF_M06_AU01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1909,67 +1917,59 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9895</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Mobile Device</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>The physical device where the application is hosted, either iOS or Android.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Mobile device</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
+          <t>This is the device where the application will be hosted.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
+          <t>CF_M06_AU01</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1977,12 +1977,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Library for building user interfaces using Javascript.</t>
+          <t>Development framework used to build the mobile application.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2037,11 +2037,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>is a library for building user interfaces using Javascript.</t>
+          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The central axis that manages the entire data flow and notifies Stores when the state needs to be modified.</t>
+          <t>The central axis that manages the entire data flow and notifies Stores when the state should be modified.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
+          <t>Communication protocol used between the mobile application and the Waapiti API.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2253,13 +2253,13 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2449,12 +2449,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M06_AU15</t>
+          <t>CF_M06_AU25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Expo</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2477,29 +2477,29 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Open source framework for native Android, iOS, and Web applications.</t>
+          <t>Library used to manage the application state.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Expo</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2509,11 +2509,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>is an open source framework for native Android, iOS and Web applications.</t>
+          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M06_AU15</t>
+          <t>CF_M06_AU25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service used for push notifications delivery.</t>
+          <t>Service used for push notifications.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2567,15 +2567,11 @@
           <t>92</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['AU_19']</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2637,7 +2633,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>An architecture for managing and flowing data in a web application, designed to replace the Model-View-Controller (MVC) pattern.</t>
+          <t>An architecture for handling and flowing data in a web application, designed to replace the Model-View-Controller (MVC) pattern.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2687,7 +2683,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2725,13 +2721,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_19']</t>
+          <t>['AU_21']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2843,7 +2839,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2881,13 +2877,13 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_19']</t>
+          <t>['AU_21']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3007,7 +3003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3055,39 +3051,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WebSocket</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Via sockets es poden rebre els logs en temps real.</t>
+          <t>Communication protocol used for real-time logs and preview.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>CF_M06_AU29</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3098,26 +3098,58 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>waapiti server, aws sns, firebase cloud messaging, apple push notification service</t>
+          <t>presentation layer, waapiti server</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Per poder implementar aquesta funcionalitat és necessari utilitzar un servei de missatgeria per cada plataforma: Firebase Cloud Messaging (FCM) per dispositius Android i Apple Push Notification Service (APNS) per dispositius iOS. [...] AWS SNS és un servei administrat el qual ofereix el lliurament de missatges dels publicadors als subscriptors.</t>
+          <t>Via sockets, logs can be received in real time.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M06_AU22</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7326</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation layer, firebase cloud messaging, apple push notification service</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The application uses Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices to receive push notifications.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8037</v>
       </c>
     </row>
   </sheetData>
@@ -3179,7 +3211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M06_AU10</t>
+          <t>CF_M06_AU11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3190,136 +3222,136 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>action, store</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
+          <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dispatcher</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.731</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M06_AU11</t>
+          <t>CF_M06_AU12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M06_AU12</t>
+          <t>CF_M06_AU13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation, user</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+          <t>Presentation: This is the layer that communicates with the user</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7607</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M06_AU13</t>
+          <t>CF_M06_AU14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>presentation, user</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Presentation: This is the layer that communicates with the user</t>
+          <t>is a library for building user interfaces using Javascript.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8952</v>
+        <v>0.7302999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M06_AU16</t>
+          <t>CF_M06_AU15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3329,13 +3361,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jest</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+          <t>is an open source framework for native Android, iOS and Web applications.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3349,13 +3381,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6788</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M06_AU17</t>
+          <t>CF_M06_AU16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3365,33 +3397,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NodeJS</t>
+          <t>Jest</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
+          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.679</v>
+        <v>0.6788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M06_AU18</t>
+          <t>CF_M06_AU17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3401,13 +3433,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>NodeJS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>it is a programming language developed and maintained by Microsoft</t>
+          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3421,13 +3453,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.6611</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M06_AU19</t>
+          <t>CF_M06_AU18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3437,13 +3469,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
+          <t>it is a programming language developed and maintained by Microsoft</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3457,116 +3489,116 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6944</v>
+        <v>0.6611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mobile Application</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The project “Development of a mobile application for a digital signage company”</t>
+          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8665</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M06_AU24</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Mobile Application</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>The project “Development of a mobile application for a digital signage company”</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mobile Device</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8665</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M06_AU24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
 content. </t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.7835</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M06_AU25</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Redux</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7194</v>
       </c>
     </row>
     <row r="13">
@@ -3594,7 +3626,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3630,12 +3662,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>WebSocket</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>0.6798</v>
+        <v>0.7111</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6389</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7419</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6552</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7755</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9527</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5714</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8875</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Presentation</t>
@@ -1252,13 +1263,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_AU03</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1299,14 +1308,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1330,13 +1336,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_AU05</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1357,7 +1361,6 @@
       <c r="D4" t="n">
         <v>0.8232</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1378,7 +1381,6 @@
           <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_19</t>
@@ -1389,7 +1391,6 @@
           <t>presentation layer, waapiti server</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1408,7 +1409,6 @@
           <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_AU30</t>
@@ -1459,14 +1459,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -1490,13 +1487,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1537,14 +1532,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1568,13 +1560,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1615,14 +1605,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1646,13 +1633,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1673,7 +1658,6 @@
       <c r="D8" t="n">
         <v>0.8976</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1694,7 +1678,6 @@
           <t>['AU_08', 'AU_06']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_18</t>
@@ -1705,7 +1688,6 @@
           <t>dispatcher, store</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1724,7 +1706,6 @@
           <t>CF_M06_AU08, CF_M06_AU07</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_AU10</t>
@@ -1755,7 +1736,6 @@
       <c r="D9" t="n">
         <v>0.9107</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1776,7 +1756,6 @@
           <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_17</t>
@@ -1787,7 +1766,6 @@
           <t>waapiti server, data layer</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1806,7 +1784,6 @@
           <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_AU28</t>
@@ -1837,7 +1814,6 @@
       <c r="D10" t="n">
         <v>0.9185</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1858,7 +1834,6 @@
           <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_16</t>
@@ -1869,7 +1844,6 @@
           <t>presentation layer, waapiti server</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1888,7 +1862,6 @@
           <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_AU27</t>
@@ -1939,14 +1912,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Mobile device</t>
@@ -1965,14 +1935,11 @@
       <c r="P11" t="n">
         <v>45</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_AU01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2018,13 +1985,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -2048,13 +2013,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2095,14 +2058,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Lazy Loading</t>
@@ -2126,13 +2086,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_P05</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2173,14 +2131,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2204,13 +2159,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU09</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2256,13 +2209,11 @@
           <t>['AU_16']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2286,13 +2237,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2333,14 +2282,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -2359,14 +2305,11 @@
       <c r="P16" t="n">
         <v>45</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2407,14 +2350,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2438,13 +2378,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_AU07</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2490,13 +2428,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2520,13 +2456,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU25</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2567,14 +2501,11 @@
           <t>92</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>AWS SNS</t>
@@ -2593,14 +2524,11 @@
       <c r="P19" t="n">
         <v>92</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M06_AU22</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2641,14 +2569,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2672,13 +2597,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2724,13 +2647,11 @@
           <t>['AU_21']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Apple Push Notification Service</t>
@@ -2749,14 +2670,11 @@
       <c r="P21" t="n">
         <v>91</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M06_AU21</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2797,14 +2715,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2828,13 +2743,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2880,13 +2793,11 @@
           <t>['AU_21']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging</t>
@@ -2905,14 +2816,11 @@
       <c r="P23" t="n">
         <v>91</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M06_AU20</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2953,14 +2861,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Action</t>
@@ -2984,13 +2889,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3064,7 +2967,6 @@
           <t>WebSocket</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Communication protocol used for real-time logs and preview.</t>
@@ -3095,7 +2997,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>presentation layer, waapiti server</t>
@@ -3111,7 +3012,6 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.7326</v>
       </c>
@@ -3127,7 +3027,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, firebase cloud messaging, apple push notification service</t>
@@ -3219,7 +3118,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3235,7 +3133,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.8439</v>
       </c>
@@ -3256,7 +3153,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -3287,7 +3183,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -3328,7 +3223,6 @@
           <t>React</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>is a library for building user interfaces using Javascript.</t>
@@ -3364,7 +3258,6 @@
           <t>Expo</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>is an open source framework for native Android, iOS and Web applications.</t>
@@ -3400,7 +3293,6 @@
           <t>Jest</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
@@ -3436,7 +3328,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
@@ -3472,7 +3363,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>it is a programming language developed and maintained by Microsoft</t>
@@ -3508,7 +3398,6 @@
           <t>NestJS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
@@ -3544,7 +3433,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -3580,7 +3468,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
@@ -3612,7 +3499,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -3654,7 +3540,6 @@
           <t>Socket</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>the content according to the messages that it sends.</t>
